--- a/projecto_centralizar/frontend/public/templates/contacts_import_template.xlsx
+++ b/projecto_centralizar/frontend/public/templates/contacts_import_template.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t xml:space="preserve">empresa</t>
   </si>
@@ -40,6 +40,12 @@
     <t xml:space="preserve">telefono</t>
   </si>
   <si>
+    <t xml:space="preserve">cargo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">campaña</t>
+  </si>
+  <si>
     <t xml:space="preserve">Acme SL</t>
   </si>
   <si>
@@ -55,6 +61,12 @@
     <t xml:space="preserve">https://linkedin.com/in/juan</t>
   </si>
   <si>
+    <t xml:space="preserve">CEO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campaña 10</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tech Corp</t>
   </si>
   <si>
@@ -68,6 +80,12 @@
   </si>
   <si>
     <t xml:space="preserve">https://linkedin.com/in/maria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Head of Sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campaña20</t>
   </si>
 </sst>
 </file>
@@ -82,6 +100,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -103,6 +122,7 @@
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -147,12 +167,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -279,71 +303,90 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="17.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="24.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="17.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="24.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14.74"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="0" t="n">
+      <c r="D2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="1" t="n">
         <v>123456789</v>
+      </c>
+      <c r="G2" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="0" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="0" t="n">
+      <c r="B3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="1" t="n">
         <v>999888777</v>
+      </c>
+      <c r="G3" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="0" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/projecto_centralizar/frontend/public/templates/contacts_import_template.xlsx
+++ b/projecto_centralizar/frontend/public/templates/contacts_import_template.xlsx
@@ -22,28 +22,28 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
-    <t xml:space="preserve">empresa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nombre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">apellido</t>
-  </si>
-  <si>
-    <t xml:space="preserve">email</t>
-  </si>
-  <si>
-    <t xml:space="preserve">linkedin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">telefono</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cargo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">campaña</t>
+    <t xml:space="preserve">Nombre empresa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apellidos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LinkedIn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Telefono</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cargo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campaña</t>
   </si>
   <si>
     <t xml:space="preserve">Acme SL</t>
@@ -85,7 +85,7 @@
     <t xml:space="preserve">Head of Sales</t>
   </si>
   <si>
-    <t xml:space="preserve">Campaña20</t>
+    <t xml:space="preserve">Campaña 20</t>
   </si>
 </sst>
 </file>
@@ -306,9 +306,10 @@
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="17.24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="24.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14.74"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -330,10 +331,10 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -356,10 +357,10 @@
       <c r="F2" s="1" t="n">
         <v>123456789</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="0" t="s">
+      <c r="H2" s="1" t="s">
         <v>14</v>
       </c>
     </row>
@@ -382,10 +383,10 @@
       <c r="F3" s="1" t="n">
         <v>999888777</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="G3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="0" t="s">
+      <c r="H3" s="1" t="s">
         <v>21</v>
       </c>
     </row>
